--- a/14_extratask/03_Clinic/03予約フロー.xlsx
+++ b/14_extratask/03_Clinic/03予約フロー.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\f-otsuka\Desktop\workspace\14_extratask\03_Clinic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2FA6FEC-BE49-4C70-8DD9-2EE0C223FAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AE8E8E-430D-4DDF-8DBB-0841CEF17D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{6219F1B8-6B15-48ED-ABCE-B11D0A54E502}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6219F1B8-6B15-48ED-ABCE-B11D0A54E502}"/>
   </bookViews>
   <sheets>
     <sheet name="クリニック側" sheetId="1" r:id="rId1"/>
@@ -146,11 +146,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8045,6 +8045,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ED3DF35-9F76-42B1-9C59-7C4D646CBD76}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:F65"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -8387,12 +8390,16 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0639FE4-5EC2-403E-98EB-8B1644AA9D6B}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:F59"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -8404,356 +8411,356 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
       <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="F3" s="7"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="F7" s="7"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="F8" s="6"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="F9" s="6"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="F10" s="6"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="F11" s="6"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="F14" s="6"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="F20" s="6"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="F21" s="6"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="F22" s="6"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="F24" s="6"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="F25" s="6"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="F26" s="7"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="F26" s="6"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="F27" s="7"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="F27" s="6"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="F28" s="7"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="F28" s="6"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="F29" s="7"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="F29" s="6"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="F30" s="7"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="F30" s="6"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="F31" s="7"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="F31" s="6"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="F32" s="7"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="F32" s="6"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="F33" s="7"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="F33" s="6"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="F34" s="7"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="F34" s="6"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="F35" s="7"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="F35" s="6"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="F36" s="7"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="F36" s="6"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="F37" s="7"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="F37" s="6"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="F38" s="7"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="F38" s="6"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="F39" s="7"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="F39" s="6"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="F40" s="7"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="F40" s="6"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="F41" s="7"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="F41" s="6"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="F42" s="7"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="F42" s="6"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="F43" s="7"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="F43" s="6"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="F44" s="7"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="F44" s="6"/>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="F45" s="7"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="F45" s="6"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="F46" s="7"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="F46" s="6"/>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="F47" s="7"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="F47" s="6"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="F48" s="7"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="F48" s="6"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="F49" s="7"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="F49" s="6"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="F50" s="7"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="F50" s="6"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="F51" s="7"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="F51" s="6"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="F52" s="7"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="F52" s="6"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="F53" s="7"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="F53" s="6"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="F54" s="7"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="F54" s="6"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="F55" s="7"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="F55" s="6"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="F56" s="7"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="F56" s="6"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="F57" s="7"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="F57" s="6"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="F58" s="7"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="F58" s="6"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="F59" s="7"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="F59" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8761,6 +8768,7 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="74" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>